--- a/racecards/racecard_20260531.xlsx
+++ b/racecards/racecard_20260531.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO160"/>
+  <dimension ref="A1:AO159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,7 +671,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>1</v>
@@ -739,10 +743,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1134</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -830,7 +836,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>2</v>
@@ -902,10 +912,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>929</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -993,7 +1005,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>3</v>
@@ -1061,7 +1077,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1026</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>-</t>
@@ -1150,7 +1168,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>4</v>
@@ -1218,7 +1240,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1132</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>-</t>
@@ -1307,7 +1331,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>5</v>
@@ -1379,7 +1407,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1206</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>-</t>
@@ -1468,7 +1498,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>6</v>
@@ -1540,10 +1574,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1127</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -1631,7 +1667,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>7</v>
@@ -1699,10 +1739,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1086</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -1790,7 +1832,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>8</v>
@@ -1858,10 +1904,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1103</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
@@ -1949,7 +1997,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>9</v>
@@ -2017,10 +2069,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1100</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -2108,7 +2162,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>10</v>
@@ -2180,10 +2238,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1108</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -2271,7 +2331,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>11</v>
@@ -2343,7 +2407,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1050</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
           <t>-</t>
@@ -2432,7 +2498,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>12</v>
@@ -2500,7 +2570,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1118</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
           <t>-</t>
@@ -2589,7 +2661,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>13</v>
@@ -2657,10 +2733,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1001</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
@@ -2748,7 +2826,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>14</v>
@@ -2820,10 +2902,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1097</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
@@ -2909,7 +2993,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -2987,10 +3075,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1140</v>
+      </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -3080,7 +3170,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -3158,10 +3252,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1149</v>
+      </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -3251,7 +3347,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -3329,10 +3429,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>1156</v>
+      </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -3422,7 +3524,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -3500,10 +3606,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>1263</v>
+      </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -3593,7 +3701,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -3671,10 +3783,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>1091</v>
+      </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -3764,7 +3878,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -3842,7 +3960,9 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>1078</v>
+      </c>
       <c r="AD21" t="inlineStr">
         <is>
           <t>-</t>
@@ -3929,7 +4049,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4003,7 +4127,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>1237</v>
+      </c>
       <c r="AD22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4090,7 +4216,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4168,7 +4298,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>1125</v>
+      </c>
       <c r="AD23" t="inlineStr">
         <is>
           <t>-</t>
@@ -4255,7 +4387,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4329,7 +4465,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>1136</v>
+      </c>
       <c r="AD24" t="inlineStr">
         <is>
           <t>-</t>
@@ -4416,7 +4554,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4494,10 +4636,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>1182</v>
+      </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+15</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -4587,7 +4731,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4665,7 +4813,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>1164</v>
+      </c>
       <c r="AD26" t="inlineStr">
         <is>
           <t>-</t>
@@ -4752,7 +4902,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4830,10 +4984,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>1055</v>
+      </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -4923,7 +5079,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5001,10 +5161,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr"/>
+      <c r="AC28" t="n">
+        <v>1179</v>
+      </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -5094,7 +5256,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5176,10 +5342,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>1075</v>
+      </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
@@ -5269,7 +5437,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5321,7 +5493,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>1127</v>
+      </c>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
@@ -5380,7 +5554,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5432,7 +5610,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>1213</v>
+      </c>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
@@ -5491,7 +5671,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5569,10 +5753,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>1145</v>
+      </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
@@ -5662,7 +5848,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5740,10 +5930,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr"/>
+      <c r="AC33" t="n">
+        <v>1166</v>
+      </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -5833,7 +6025,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5911,10 +6107,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>1042</v>
+      </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -6004,7 +6202,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6082,10 +6284,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>1203</v>
+      </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
@@ -6175,7 +6379,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6249,10 +6457,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>1206</v>
+      </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
@@ -6342,7 +6552,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6420,10 +6634,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>1164</v>
+      </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
@@ -6513,7 +6729,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6591,10 +6811,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>1110</v>
+      </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
@@ -6684,7 +6906,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6758,10 +6984,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr"/>
+      <c r="AC39" t="n">
+        <v>1061</v>
+      </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
@@ -6851,7 +7079,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6929,10 +7161,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>1040</v>
+      </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
@@ -7022,7 +7256,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7100,10 +7338,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr"/>
+      <c r="AC41" t="n">
+        <v>1132</v>
+      </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
@@ -7193,7 +7433,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7271,10 +7515,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>1231</v>
+      </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
@@ -7364,7 +7610,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7442,10 +7692,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>1163</v>
+      </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
@@ -7535,7 +7787,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7613,10 +7869,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr"/>
+      <c r="AC44" t="n">
+        <v>1200</v>
+      </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
@@ -7706,7 +7964,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7784,10 +8046,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr"/>
+      <c r="AC45" t="n">
+        <v>1118</v>
+      </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
@@ -7877,7 +8141,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7929,7 +8197,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr"/>
+      <c r="AC46" t="n">
+        <v>1109</v>
+      </c>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
@@ -7988,7 +8258,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8036,7 +8310,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr"/>
+      <c r="AC47" t="n">
+        <v>1144</v>
+      </c>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
@@ -8095,7 +8371,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8169,10 +8449,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>1101</v>
+      </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
@@ -8262,7 +8544,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8340,10 +8626,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr"/>
+      <c r="AC49" t="n">
+        <v>1191</v>
+      </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
@@ -8433,7 +8721,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8511,10 +8803,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>1266</v>
+      </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+16</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
@@ -8604,7 +8898,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8682,10 +8980,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr"/>
+      <c r="AC51" t="n">
+        <v>1106</v>
+      </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
@@ -8775,7 +9075,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8853,10 +9157,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr"/>
+      <c r="AC52" t="n">
+        <v>1121</v>
+      </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
@@ -8946,7 +9252,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9024,10 +9334,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr"/>
+      <c r="AC53" t="n">
+        <v>1111</v>
+      </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
@@ -9117,7 +9429,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9195,10 +9511,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr"/>
+      <c r="AC54" t="n">
+        <v>1109</v>
+      </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
@@ -9288,7 +9606,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9366,10 +9688,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>1214</v>
+      </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+22</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -9455,7 +9779,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9533,10 +9861,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr"/>
+      <c r="AC56" t="n">
+        <v>1194</v>
+      </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr">
@@ -9626,7 +9956,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9700,10 +10034,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr"/>
+      <c r="AC57" t="n">
+        <v>1171</v>
+      </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
@@ -9793,7 +10129,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9871,10 +10211,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr"/>
+      <c r="AC58" t="n">
+        <v>1157</v>
+      </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr">
@@ -9964,7 +10306,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -10042,10 +10388,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr"/>
+      <c r="AC59" t="n">
+        <v>1108</v>
+      </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
@@ -10135,7 +10483,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -10217,10 +10569,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr"/>
+      <c r="AC60" t="n">
+        <v>1110</v>
+      </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
@@ -10310,7 +10664,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -10388,10 +10746,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr"/>
+      <c r="AC61" t="n">
+        <v>1223</v>
+      </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -10477,7 +10837,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -10529,7 +10893,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>1126</v>
+      </c>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
@@ -10588,7 +10954,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -10640,7 +11010,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr"/>
+      <c r="AC63" t="n">
+        <v>1056</v>
+      </c>
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
@@ -10699,7 +11071,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -10777,10 +11153,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr"/>
+      <c r="AC64" t="n">
+        <v>1137</v>
+      </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
@@ -10870,7 +11248,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -10948,10 +11330,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr"/>
+      <c r="AC65" t="n">
+        <v>1131</v>
+      </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
@@ -11041,7 +11425,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -11119,10 +11507,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr"/>
+      <c r="AC66" t="n">
+        <v>1121</v>
+      </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -11208,7 +11598,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -11286,10 +11680,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>1098</v>
+      </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr">
@@ -11379,7 +11775,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -11457,10 +11857,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr"/>
+      <c r="AC68" t="n">
+        <v>1239</v>
+      </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr"/>
@@ -11546,7 +11948,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -11620,10 +12026,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr"/>
+      <c r="AC69" t="n">
+        <v>1026</v>
+      </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
@@ -11713,7 +12121,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -11791,10 +12203,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr"/>
+      <c r="AC70" t="n">
+        <v>1111</v>
+      </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
@@ -11884,7 +12298,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -11962,10 +12380,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr"/>
+      <c r="AC71" t="n">
+        <v>1129</v>
+      </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
@@ -12055,7 +12475,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -12133,10 +12557,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr"/>
+      <c r="AC72" t="n">
+        <v>1000</v>
+      </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
@@ -12226,7 +12652,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -12300,10 +12730,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr"/>
+      <c r="AC73" t="n">
+        <v>1031</v>
+      </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
@@ -12393,7 +12825,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -12471,10 +12907,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr"/>
+      <c r="AC74" t="n">
+        <v>1075</v>
+      </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
@@ -12564,7 +13002,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -12642,10 +13084,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr"/>
+      <c r="AC75" t="n">
+        <v>1090</v>
+      </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
@@ -12735,7 +13179,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -12817,10 +13265,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr"/>
+      <c r="AC76" t="n">
+        <v>1079</v>
+      </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
@@ -12910,7 +13360,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -12988,10 +13442,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr"/>
+      <c r="AC77" t="n">
+        <v>1010</v>
+      </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
@@ -13081,7 +13537,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -13159,10 +13619,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>1053</v>
+      </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
@@ -13252,7 +13714,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -13330,10 +13796,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>1111</v>
+      </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr"/>
@@ -13419,7 +13887,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -13493,10 +13965,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr"/>
+      <c r="AC80" t="n">
+        <v>1061</v>
+      </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE80" t="inlineStr">
@@ -13586,7 +14060,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -13664,10 +14142,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>1136</v>
+      </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
@@ -13757,7 +14237,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -13835,10 +14319,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr"/>
+      <c r="AC82" t="n">
+        <v>1106</v>
+      </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE82" t="inlineStr">
@@ -13928,7 +14414,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -14006,10 +14496,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr"/>
+      <c r="AC83" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
@@ -14099,7 +14591,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -14177,10 +14673,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr"/>
+      <c r="AC84" t="n">
+        <v>1213</v>
+      </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE84" t="inlineStr"/>
@@ -14266,7 +14764,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -14340,10 +14842,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr"/>
+      <c r="AC85" t="n">
+        <v>1040</v>
+      </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
@@ -14433,7 +14937,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -14511,10 +15019,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr"/>
+      <c r="AC86" t="n">
+        <v>1181</v>
+      </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE86" t="inlineStr"/>
@@ -14600,7 +15110,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -14678,10 +15192,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr"/>
+      <c r="AC87" t="n">
+        <v>1170</v>
+      </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr"/>
@@ -14767,7 +15283,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -14845,10 +15365,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr"/>
+      <c r="AC88" t="n">
+        <v>1116</v>
+      </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
@@ -14938,7 +15460,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -15012,10 +15538,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr"/>
+      <c r="AC89" t="n">
+        <v>1156</v>
+      </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
@@ -15105,7 +15633,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -15183,10 +15715,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr"/>
+      <c r="AC90" t="n">
+        <v>1199</v>
+      </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
@@ -15276,7 +15810,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -15350,10 +15888,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr"/>
+      <c r="AC91" t="n">
+        <v>1126</v>
+      </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE91" t="inlineStr"/>
@@ -15439,7 +15979,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -15491,7 +16035,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr"/>
+      <c r="AC92" t="n">
+        <v>1120</v>
+      </c>
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr"/>
@@ -15550,7 +16096,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -15602,7 +16152,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr"/>
+      <c r="AC93" t="n">
+        <v>1127</v>
+      </c>
       <c r="AD93" t="inlineStr"/>
       <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr"/>
@@ -15663,7 +16215,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="n">
         <v>1</v>
@@ -15733,10 +16289,12 @@
         </is>
       </c>
       <c r="AB94" t="inlineStr"/>
-      <c r="AC94" t="inlineStr"/>
+      <c r="AC94" t="n">
+        <v>1119</v>
+      </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE94" t="inlineStr">
@@ -15828,7 +16386,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="n">
         <v>2</v>
@@ -15894,10 +16456,12 @@
       </c>
       <c r="AA95" t="inlineStr"/>
       <c r="AB95" t="inlineStr"/>
-      <c r="AC95" t="inlineStr"/>
+      <c r="AC95" t="n">
+        <v>1105</v>
+      </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE95" t="inlineStr">
@@ -15989,7 +16553,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="n">
         <v>3</v>
@@ -16059,10 +16627,12 @@
         </is>
       </c>
       <c r="AB96" t="inlineStr"/>
-      <c r="AC96" t="inlineStr"/>
+      <c r="AC96" t="n">
+        <v>1164</v>
+      </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE96" t="inlineStr">
@@ -16154,7 +16724,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="n">
         <v>4</v>
@@ -16224,10 +16798,12 @@
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
-      <c r="AC97" t="inlineStr"/>
+      <c r="AC97" t="n">
+        <v>1044</v>
+      </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
@@ -16319,7 +16895,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="n">
         <v>5</v>
@@ -16389,10 +16969,12 @@
         </is>
       </c>
       <c r="AB98" t="inlineStr"/>
-      <c r="AC98" t="inlineStr"/>
+      <c r="AC98" t="n">
+        <v>1219</v>
+      </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
@@ -16484,7 +17066,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
         <v>6</v>
@@ -16554,10 +17140,12 @@
         </is>
       </c>
       <c r="AB99" t="inlineStr"/>
-      <c r="AC99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>1187</v>
+      </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-21</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr"/>
@@ -16645,7 +17233,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
         <v>7</v>
@@ -16711,10 +17303,12 @@
       </c>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
-      <c r="AC100" t="inlineStr"/>
+      <c r="AC100" t="n">
+        <v>1115</v>
+      </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
@@ -16806,7 +17400,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
         <v>8</v>
@@ -16876,10 +17474,12 @@
         </is>
       </c>
       <c r="AB101" t="inlineStr"/>
-      <c r="AC101" t="inlineStr"/>
+      <c r="AC101" t="n">
+        <v>1074</v>
+      </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE101" t="inlineStr">
@@ -16971,7 +17571,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="n">
         <v>9</v>
@@ -17041,10 +17645,12 @@
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
-      <c r="AC102" t="inlineStr"/>
+      <c r="AC102" t="n">
+        <v>1275</v>
+      </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
@@ -17216,10 +17822,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr"/>
+      <c r="AC103" t="n">
+        <v>1088</v>
+      </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
@@ -17387,10 +17995,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr"/>
+      <c r="AC104" t="n">
+        <v>1190</v>
+      </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
@@ -17562,10 +18172,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr"/>
+      <c r="AC105" t="n">
+        <v>1049</v>
+      </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE105" t="inlineStr">
@@ -17737,10 +18349,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr"/>
+      <c r="AC106" t="n">
+        <v>1111</v>
+      </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
@@ -17912,10 +18526,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr"/>
+      <c r="AC107" t="n">
+        <v>1050</v>
+      </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
@@ -18087,10 +18703,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr"/>
+      <c r="AC108" t="n">
+        <v>1161</v>
+      </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
@@ -18262,10 +18880,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr"/>
+      <c r="AC109" t="n">
+        <v>1128</v>
+      </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
@@ -18437,10 +19057,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr"/>
+      <c r="AC110" t="n">
+        <v>1084</v>
+      </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
@@ -18612,7 +19234,9 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr"/>
+      <c r="AC111" t="n">
+        <v>1117</v>
+      </c>
       <c r="AD111" t="inlineStr">
         <is>
           <t>-</t>
@@ -18781,10 +19405,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr"/>
+      <c r="AC112" t="n">
+        <v>1134</v>
+      </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr"/>
@@ -18952,10 +19578,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr"/>
+      <c r="AC113" t="n">
+        <v>1132</v>
+      </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE113" t="inlineStr">
@@ -19127,10 +19755,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr"/>
+      <c r="AC114" t="n">
+        <v>1119</v>
+      </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE114" t="inlineStr">
@@ -19302,10 +19932,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr"/>
+      <c r="AC115" t="n">
+        <v>1129</v>
+      </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE115" t="inlineStr"/>
@@ -19473,10 +20105,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr"/>
+      <c r="AC116" t="n">
+        <v>1022</v>
+      </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
@@ -19622,7 +20256,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr"/>
+      <c r="AC117" t="n">
+        <v>1276</v>
+      </c>
       <c r="AD117" t="inlineStr"/>
       <c r="AE117" t="inlineStr"/>
       <c r="AF117" t="inlineStr"/>
@@ -19737,7 +20373,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr"/>
+      <c r="AC118" t="n">
+        <v>1171</v>
+      </c>
       <c r="AD118" t="inlineStr"/>
       <c r="AE118" t="inlineStr"/>
       <c r="AF118" t="inlineStr"/>
@@ -19798,7 +20436,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="n">
         <v>1</v>
@@ -19868,10 +20510,12 @@
         </is>
       </c>
       <c r="AB119" t="inlineStr"/>
-      <c r="AC119" t="inlineStr"/>
+      <c r="AC119" t="n">
+        <v>1119</v>
+      </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
@@ -19963,7 +20607,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="n">
         <v>2</v>
@@ -20033,10 +20681,12 @@
         </is>
       </c>
       <c r="AB120" t="inlineStr"/>
-      <c r="AC120" t="inlineStr"/>
+      <c r="AC120" t="n">
+        <v>1173</v>
+      </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE120" t="inlineStr">
@@ -20128,7 +20778,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="n">
         <v>3</v>
@@ -20198,10 +20852,12 @@
         </is>
       </c>
       <c r="AB121" t="inlineStr"/>
-      <c r="AC121" t="inlineStr"/>
+      <c r="AC121" t="n">
+        <v>1196</v>
+      </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE121" t="inlineStr">
@@ -20293,7 +20949,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="n">
         <v>4</v>
@@ -20359,10 +21019,12 @@
       </c>
       <c r="AA122" t="inlineStr"/>
       <c r="AB122" t="inlineStr"/>
-      <c r="AC122" t="inlineStr"/>
+      <c r="AC122" t="n">
+        <v>1218</v>
+      </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE122" t="inlineStr">
@@ -20454,7 +21116,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="n">
         <v>5</v>
@@ -20524,10 +21190,12 @@
         </is>
       </c>
       <c r="AB123" t="inlineStr"/>
-      <c r="AC123" t="inlineStr"/>
+      <c r="AC123" t="n">
+        <v>1148</v>
+      </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
@@ -20619,7 +21287,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="n">
         <v>6</v>
@@ -20685,10 +21357,12 @@
       </c>
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="inlineStr"/>
-      <c r="AC124" t="inlineStr"/>
+      <c r="AC124" t="n">
+        <v>1171</v>
+      </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
@@ -20780,7 +21454,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="n">
         <v>7</v>
@@ -20850,10 +21528,12 @@
         </is>
       </c>
       <c r="AB125" t="inlineStr"/>
-      <c r="AC125" t="inlineStr"/>
+      <c r="AC125" t="n">
+        <v>1181</v>
+      </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
@@ -20945,7 +21625,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="n">
         <v>8</v>
@@ -21015,10 +21699,12 @@
         </is>
       </c>
       <c r="AB126" t="inlineStr"/>
-      <c r="AC126" t="inlineStr"/>
+      <c r="AC126" t="n">
+        <v>1084</v>
+      </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE126" t="inlineStr">
@@ -21110,7 +21796,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
         <v>9</v>
@@ -21184,10 +21874,12 @@
         </is>
       </c>
       <c r="AB127" t="inlineStr"/>
-      <c r="AC127" t="inlineStr"/>
+      <c r="AC127" t="n">
+        <v>1226</v>
+      </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
@@ -21279,7 +21971,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="n">
         <v>10</v>
@@ -21349,10 +22045,12 @@
         </is>
       </c>
       <c r="AB128" t="inlineStr"/>
-      <c r="AC128" t="inlineStr"/>
+      <c r="AC128" t="n">
+        <v>1181</v>
+      </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE128" t="inlineStr">
@@ -21442,7 +22140,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -21520,10 +22222,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr"/>
+      <c r="AC129" t="n">
+        <v>1200</v>
+      </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE129" t="inlineStr">
@@ -21613,7 +22317,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -21691,10 +22399,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr"/>
+      <c r="AC130" t="n">
+        <v>1056</v>
+      </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE130" t="inlineStr">
@@ -21784,7 +22494,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -21862,10 +22576,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr"/>
+      <c r="AC131" t="n">
+        <v>1167</v>
+      </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="AE131" t="inlineStr">
@@ -21955,7 +22671,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22033,10 +22753,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr"/>
+      <c r="AC132" t="n">
+        <v>1197</v>
+      </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
@@ -22126,7 +22848,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22204,10 +22930,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr"/>
+      <c r="AC133" t="n">
+        <v>1173</v>
+      </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE133" t="inlineStr">
@@ -22297,7 +23025,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22371,10 +23103,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC134" t="inlineStr"/>
+      <c r="AC134" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE134" t="inlineStr">
@@ -22464,7 +23198,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22542,10 +23280,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr"/>
+      <c r="AC135" t="n">
+        <v>1000</v>
+      </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE135" t="inlineStr">
@@ -22635,7 +23375,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22713,10 +23457,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr"/>
+      <c r="AC136" t="n">
+        <v>1117</v>
+      </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE136" t="inlineStr"/>
@@ -22802,7 +23548,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22880,10 +23630,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr"/>
+      <c r="AC137" t="n">
+        <v>1086</v>
+      </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE137" t="inlineStr">
@@ -22973,7 +23725,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -23051,7 +23807,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr"/>
+      <c r="AC138" t="n">
+        <v>1177</v>
+      </c>
       <c r="AD138" t="inlineStr">
         <is>
           <t>-</t>
@@ -23138,7 +23896,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -23220,10 +23982,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr"/>
+      <c r="AC139" t="n">
+        <v>1162</v>
+      </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+15</t>
         </is>
       </c>
       <c r="AE139" t="inlineStr">
@@ -23313,7 +24077,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -23391,10 +24159,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr"/>
+      <c r="AC140" t="n">
+        <v>1140</v>
+      </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr"/>
@@ -23480,7 +24250,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -23558,10 +24332,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr"/>
+      <c r="AC141" t="n">
+        <v>1036</v>
+      </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+19</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr">
@@ -23651,7 +24427,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -23733,10 +24513,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr"/>
+      <c r="AC142" t="n">
+        <v>1028</v>
+      </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+14</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
@@ -23826,7 +24608,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J143" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -23878,7 +24664,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC143" t="inlineStr"/>
+      <c r="AC143" t="n">
+        <v>1218</v>
+      </c>
       <c r="AD143" t="inlineStr"/>
       <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr"/>
@@ -23937,7 +24725,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J144" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -23985,7 +24777,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr"/>
+      <c r="AC144" t="n">
+        <v>1085</v>
+      </c>
       <c r="AD144" t="inlineStr"/>
       <c r="AE144" t="inlineStr"/>
       <c r="AF144" t="inlineStr"/>
@@ -24044,7 +24838,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J145" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -24122,10 +24920,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr"/>
+      <c r="AC145" t="n">
+        <v>1237</v>
+      </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE145" t="inlineStr">
@@ -24215,7 +25015,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J146" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -24293,10 +25097,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC146" t="inlineStr"/>
+      <c r="AC146" t="n">
+        <v>1203</v>
+      </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr">
@@ -24386,7 +25192,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -24397,17 +25207,17 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>GOLD PATCH</t>
+          <t>CALA DEI MORI</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>HK_2025_L099</t>
+          <t>HK_2025_L428</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>L099</t>
+          <t>L428</t>
         </is>
       </c>
       <c r="O147" t="n">
@@ -24421,18 +25231,18 @@
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>C S Shum</t>
         </is>
       </c>
       <c r="S147" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="T147" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
@@ -24451,30 +25261,28 @@
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>3/1/1/3/1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>XB</t>
+          <t>TT1</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>+ 1</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC147" t="n">
+        <v>1034</v>
+      </c>
       <c r="AD147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>1.08.50</t>
-        </is>
-      </c>
+      <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="inlineStr">
         <is>
           <t>-</t>
@@ -24482,30 +25290,28 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>2,700,450</t>
-        </is>
-      </c>
-      <c r="AH147" t="n">
-        <v>22</v>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr"/>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>Patch Syndicate</t>
+          <t>Raymond Hui</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>Ardrossan</t>
+          <t>Dandy Man</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>La Donna</t>
+          <t>My Excelsa</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="AM147" t="b">
@@ -24557,7 +25363,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -24635,10 +25445,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr"/>
+      <c r="AC148" t="n">
+        <v>1112</v>
+      </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
@@ -24728,7 +25540,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J149" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -24806,10 +25622,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr"/>
+      <c r="AC149" t="n">
+        <v>1077</v>
+      </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE149" t="inlineStr">
@@ -24899,7 +25717,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J150" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -24977,10 +25799,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr"/>
+      <c r="AC150" t="n">
+        <v>1149</v>
+      </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE150" t="inlineStr"/>
@@ -25066,7 +25890,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J151" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -25144,10 +25972,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr"/>
+      <c r="AC151" t="n">
+        <v>1207</v>
+      </c>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE151" t="inlineStr">
@@ -25237,7 +26067,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J152" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -25315,10 +26149,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr"/>
+      <c r="AC152" t="n">
+        <v>1189</v>
+      </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE152" t="inlineStr">
@@ -25408,7 +26244,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -25486,7 +26326,9 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr"/>
+      <c r="AC153" t="n">
+        <v>1131</v>
+      </c>
       <c r="AD153" t="inlineStr">
         <is>
           <t>-</t>
@@ -25573,7 +26415,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -25651,10 +26497,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr"/>
+      <c r="AC154" t="n">
+        <v>1017</v>
+      </c>
       <c r="AD154" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE154" t="inlineStr"/>
@@ -25740,7 +26588,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -25818,10 +26670,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC155" t="inlineStr"/>
+      <c r="AC155" t="n">
+        <v>1105</v>
+      </c>
       <c r="AD155" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE155" t="inlineStr">
@@ -25911,7 +26765,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -25985,10 +26843,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr"/>
+      <c r="AC156" t="n">
+        <v>1048</v>
+      </c>
       <c r="AD156" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE156" t="inlineStr">
@@ -26078,7 +26938,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -26156,10 +27020,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr"/>
+      <c r="AC157" t="n">
+        <v>1079</v>
+      </c>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE157" t="inlineStr">
@@ -26249,7 +27115,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -26323,10 +27193,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr"/>
+      <c r="AC158" t="n">
+        <v>1106</v>
+      </c>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE158" t="inlineStr">
@@ -26416,18 +27288,22 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J159" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CALA DEI MORI</t>
+          <t>JUMBO TREASURE</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
@@ -26437,30 +27313,30 @@
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr">
         <is>
-          <t>C S Shum</t>
+          <t>W K Mo</t>
         </is>
       </c>
       <c r="S159" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T159" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
       <c r="W159" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr"/>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8/3/4/12/1/11</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>TT1</t>
+          <t>CP/TT</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
@@ -26468,7 +27344,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC159" t="inlineStr"/>
+      <c r="AC159" t="n">
+        <v>1112</v>
+      </c>
       <c r="AD159" t="inlineStr"/>
       <c r="AE159" t="inlineStr"/>
       <c r="AF159" t="inlineStr"/>
@@ -26487,117 +27365,6 @@
         </is>
       </c>
       <c r="AO159" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>11</v>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>HONG KONG KA YING (MEIZHOU) GENERAL CHAMBER OF COMMERCE CUP HANDICAP</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>3</v>
-      </c>
-      <c r="F160" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>80-60</t>
-        </is>
-      </c>
-      <c r="K160" t="n">
-        <v>2</v>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>JUMBO TREASURE</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>W K Mo</t>
-        </is>
-      </c>
-      <c r="S160" t="n">
-        <v>126</v>
-      </c>
-      <c r="T160" t="n">
-        <v>71</v>
-      </c>
-      <c r="U160" t="inlineStr"/>
-      <c r="V160" t="inlineStr"/>
-      <c r="W160" t="n">
-        <v>5</v>
-      </c>
-      <c r="X160" t="inlineStr"/>
-      <c r="Y160" t="inlineStr"/>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>8/3/4/12/1/11</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>CP/TT</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr"/>
-      <c r="AD160" t="inlineStr"/>
-      <c r="AE160" t="inlineStr"/>
-      <c r="AF160" t="inlineStr"/>
-      <c r="AG160" t="inlineStr"/>
-      <c r="AH160" t="inlineStr"/>
-      <c r="AI160" t="inlineStr"/>
-      <c r="AJ160" t="inlineStr"/>
-      <c r="AK160" t="inlineStr"/>
-      <c r="AL160" t="inlineStr"/>
-      <c r="AM160" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN160" t="inlineStr">
-        <is>
-          <t>HK$1,860,000,</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
         <is>
           <t>18:20</t>
         </is>
@@ -26861,7 +27628,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>1</v>
@@ -26931,10 +27702,12 @@
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1119</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -27026,7 +27799,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>2</v>
@@ -27096,10 +27873,12 @@
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1173</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -27191,7 +27970,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>3</v>
@@ -27261,10 +28044,12 @@
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1196</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -27356,7 +28141,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>4</v>
@@ -27422,10 +28211,12 @@
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1218</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -27517,7 +28308,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>5</v>
@@ -27587,10 +28382,12 @@
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1148</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -27682,7 +28479,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>6</v>
@@ -27748,10 +28549,12 @@
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1171</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -27843,7 +28646,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>7</v>
@@ -27913,10 +28720,12 @@
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1181</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -28008,7 +28817,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>8</v>
@@ -28078,10 +28891,12 @@
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1084</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -28173,7 +28988,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>9</v>
@@ -28247,10 +29066,12 @@
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1226</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -28342,7 +29163,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>10</v>
@@ -28412,10 +29237,12 @@
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1181</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -28726,7 +29553,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -28804,10 +29635,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1200</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -28897,7 +29730,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -28975,10 +29812,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1056</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -29068,7 +29907,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -29146,10 +29989,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1167</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -29239,7 +30084,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -29317,10 +30166,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1197</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -29410,7 +30261,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -29488,10 +30343,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1173</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -29581,7 +30438,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -29655,10 +30516,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -29748,7 +30611,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -29826,10 +30693,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -29919,7 +30788,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -29997,10 +30870,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1117</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
@@ -30086,7 +30961,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -30164,10 +31043,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1086</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -30257,7 +31138,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -30335,7 +31220,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1177</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>-</t>
@@ -30422,7 +31309,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -30504,10 +31395,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1162</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -30597,7 +31490,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -30675,10 +31572,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1140</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -30764,7 +31663,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -30842,10 +31745,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1036</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+19</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -30935,7 +31840,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -31017,10 +31926,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1028</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+14</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -31110,7 +32021,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -31162,7 +32077,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1218</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -31221,7 +32138,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -31269,7 +32190,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1085</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -31304,7 +32227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO17"/>
+  <dimension ref="A1:AO16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31549,7 +32472,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -31627,10 +32554,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1237</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -31720,7 +32649,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -31798,10 +32731,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1203</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -31891,7 +32826,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -31902,17 +32841,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>GOLD PATCH</t>
+          <t>CALA DEI MORI</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>HK_2025_L099</t>
+          <t>HK_2025_L428</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>L099</t>
+          <t>L428</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -31926,18 +32865,18 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>C S Shum</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="T4" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -31956,30 +32895,28 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3/1/1/3/1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>XB</t>
+          <t>TT1</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>+ 1</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>1034</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>1.08.50</t>
-        </is>
-      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
           <t>-</t>
@@ -31987,30 +32924,28 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2,700,450</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>22</v>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Patch Syndicate</t>
+          <t>Raymond Hui</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Ardrossan</t>
+          <t>Dandy Man</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>La Donna</t>
+          <t>My Excelsa</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="AM4" t="b">
@@ -32062,7 +32997,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -32140,10 +33079,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1112</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -32233,7 +33174,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -32311,10 +33256,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1077</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -32404,7 +33351,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -32482,10 +33433,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1149</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -32571,7 +33524,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -32649,10 +33606,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1207</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -32742,7 +33701,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -32820,10 +33783,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1189</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -32913,7 +33878,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -32991,7 +33960,9 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1131</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
           <t>-</t>
@@ -33078,7 +34049,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -33156,10 +34131,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1017</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -33245,7 +34222,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -33323,10 +34304,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1105</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -33416,7 +34399,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -33490,10 +34477,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1048</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -33583,7 +34572,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -33661,10 +34654,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1079</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -33754,7 +34749,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -33828,10 +34827,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1106</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -33921,18 +34922,22 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CALA DEI MORI</t>
+          <t>JUMBO TREASURE</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -33942,30 +34947,30 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>C S Shum</t>
+          <t>W K Mo</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8/3/4/12/1/11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>TT1</t>
+          <t>CP/TT</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -33973,7 +34978,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1112</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -33992,117 +34999,6 @@
         </is>
       </c>
       <c r="AO16" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>11</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HONG KONG KA YING (MEIZHOU) GENERAL CHAMBER OF COMMERCE CUP HANDICAP</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>80-60</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>JUMBO TREASURE</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>W K Mo</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>126</v>
-      </c>
-      <c r="T17" t="n">
-        <v>71</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="n">
-        <v>5</v>
-      </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8/3/4/12/1/11</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>CP/TT</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>HK$1,860,000,</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
         <is>
           <t>18:20</t>
         </is>
@@ -34366,7 +35262,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>1</v>
@@ -34434,10 +35334,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1134</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -34525,7 +35427,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>2</v>
@@ -34597,10 +35503,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>929</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -34688,7 +35596,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>3</v>
@@ -34756,7 +35668,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1026</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>-</t>
@@ -34845,7 +35759,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>4</v>
@@ -34913,7 +35831,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1132</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>-</t>
@@ -35002,7 +35922,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>5</v>
@@ -35074,7 +35998,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1206</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>-</t>
@@ -35163,7 +36089,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>6</v>
@@ -35235,10 +36165,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1127</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -35326,7 +36258,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>7</v>
@@ -35394,10 +36330,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1086</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -35485,7 +36423,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>8</v>
@@ -35553,10 +36495,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1103</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
@@ -35644,7 +36588,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>9</v>
@@ -35712,10 +36660,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1100</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -35803,7 +36753,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>10</v>
@@ -35875,10 +36829,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1108</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -35966,7 +36922,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>11</v>
@@ -36038,7 +36998,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1050</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
           <t>-</t>
@@ -36127,7 +37089,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>12</v>
@@ -36195,7 +37161,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1118</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
           <t>-</t>
@@ -36284,7 +37252,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>13</v>
@@ -36352,10 +37324,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1001</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
@@ -36443,7 +37417,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>14</v>
@@ -36515,10 +37493,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1097</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
@@ -36825,7 +37805,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -36903,10 +37887,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1140</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -36996,7 +37982,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -37074,10 +38064,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1149</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -37167,7 +38159,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -37245,10 +38241,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1156</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -37338,7 +38336,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -37416,10 +38418,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1263</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -37509,7 +38513,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -37587,10 +38595,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1091</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -37680,7 +38690,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -37758,7 +38772,9 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1078</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>-</t>
@@ -37845,7 +38861,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -37919,7 +38939,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1237</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>-</t>
@@ -38006,7 +39028,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -38084,7 +39110,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1125</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>-</t>
@@ -38171,7 +39199,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -38245,7 +39277,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1136</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
           <t>-</t>
@@ -38332,7 +39366,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -38410,10 +39448,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1182</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -38503,7 +39543,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -38581,7 +39625,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1164</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
           <t>-</t>
@@ -38668,7 +39714,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -38746,10 +39796,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1055</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -38839,7 +39891,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -38917,10 +39973,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1179</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -39010,7 +40068,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -39092,10 +40154,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1075</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -39185,7 +40249,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -39237,7 +40305,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1127</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -39296,7 +40366,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -39348,7 +40422,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1213</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -39628,7 +40704,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -39706,10 +40786,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1145</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -39799,7 +40881,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -39877,10 +40963,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1166</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -39970,7 +41058,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -40048,10 +41140,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1042</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -40141,7 +41235,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -40219,10 +41317,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1203</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -40312,7 +41412,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -40386,10 +41490,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1206</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -40479,7 +41585,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -40557,10 +41667,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1164</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -40650,7 +41762,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -40728,10 +41844,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1110</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -40821,7 +41939,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -40895,10 +42017,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1061</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -40988,7 +42112,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -41066,10 +42194,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1040</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -41159,7 +42289,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -41237,10 +42371,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1132</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -41330,7 +42466,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -41408,10 +42548,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1231</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -41501,7 +42643,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -41579,10 +42725,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1163</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -41672,7 +42820,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -41750,10 +42902,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1200</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -41843,7 +42997,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -41921,10 +43079,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1118</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -42014,7 +43174,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -42066,7 +43230,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1109</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -42125,7 +43291,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -42173,7 +43343,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1144</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -42453,7 +43625,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -42527,10 +43703,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1101</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -42620,7 +43798,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -42698,10 +43880,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1191</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -42791,7 +43975,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -42869,10 +44057,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1266</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+16</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -42962,7 +44152,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -43040,10 +44234,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1106</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -43133,7 +44329,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -43211,10 +44411,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1121</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -43304,7 +44506,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -43382,10 +44588,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1111</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -43475,7 +44683,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -43553,10 +44765,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1109</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -43646,7 +44860,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -43724,10 +44942,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1214</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+22</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
@@ -43813,7 +45033,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -43891,10 +45115,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1194</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -43984,7 +45210,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -44058,10 +45288,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1171</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -44151,7 +45383,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -44229,10 +45465,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1157</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -44322,7 +45560,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -44400,10 +45642,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1108</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -44493,7 +45737,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -44575,10 +45823,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1110</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -44668,7 +45918,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -44746,10 +46000,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1223</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
@@ -44835,7 +46091,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -44887,7 +46147,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1126</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -44946,7 +46208,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -44998,7 +46264,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1056</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -45278,7 +46546,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -45356,10 +46628,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1137</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -45449,7 +46723,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -45527,10 +46805,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1131</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -45620,7 +46900,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -45698,10 +46982,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1121</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
@@ -45787,7 +47073,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -45865,10 +47155,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1098</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -45958,7 +47250,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -46036,10 +47332,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1239</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -46125,7 +47423,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -46199,10 +47501,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1026</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -46292,7 +47596,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -46370,10 +47678,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1111</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -46463,7 +47773,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -46541,10 +47855,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1129</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -46634,7 +47950,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -46712,10 +48032,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -46805,7 +48127,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -46879,10 +48205,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1031</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -46972,7 +48300,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -47050,10 +48382,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1075</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -47143,7 +48477,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -47221,10 +48559,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1090</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -47314,7 +48654,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -47396,10 +48740,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1079</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -47489,7 +48835,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -47567,10 +48917,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1010</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -47881,7 +49233,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -47959,10 +49315,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1053</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -48052,7 +49410,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -48130,10 +49492,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1111</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -48219,7 +49583,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -48293,10 +49661,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1061</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -48386,7 +49756,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -48464,10 +49838,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1136</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -48557,7 +49933,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -48635,10 +50015,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1106</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -48728,7 +50110,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -48806,10 +50192,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -48899,7 +50287,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -48977,10 +50369,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1213</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -49066,7 +50460,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -49140,10 +50538,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1040</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -49233,7 +50633,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -49311,10 +50715,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1181</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -49400,7 +50806,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -49478,10 +50888,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1170</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -49567,7 +50979,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -49645,10 +51061,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1116</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -49738,7 +51156,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -49812,10 +51234,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1156</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -49905,7 +51329,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -49983,10 +51411,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1199</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -50076,7 +51506,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -50150,10 +51584,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1126</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
@@ -50239,7 +51675,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -50291,7 +51731,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1120</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -50350,7 +51792,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -50402,7 +51848,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1127</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -50684,7 +52132,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>1</v>
@@ -50754,10 +52206,12 @@
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1119</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -50849,7 +52303,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>2</v>
@@ -50915,10 +52373,12 @@
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1105</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -51010,7 +52470,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>3</v>
@@ -51080,10 +52544,12 @@
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1164</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -51175,7 +52641,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>4</v>
@@ -51245,10 +52715,12 @@
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1044</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -51340,7 +52812,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>5</v>
@@ -51410,10 +52886,12 @@
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1219</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -51505,7 +52983,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>6</v>
@@ -51575,10 +53057,12 @@
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1187</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-21</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -51666,7 +53150,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>7</v>
@@ -51732,10 +53220,12 @@
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1115</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -51827,7 +53317,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>8</v>
@@ -51897,10 +53391,12 @@
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1074</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -51992,7 +53488,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>9</v>
@@ -52062,10 +53562,12 @@
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1275</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -52458,10 +53960,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1088</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -52629,10 +54133,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1190</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -52804,10 +54310,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1049</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -52979,10 +54487,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1111</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -53154,10 +54664,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1050</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -53329,10 +54841,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1161</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -53504,10 +55018,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1128</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -53679,10 +55195,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1084</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -53854,7 +55372,9 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1117</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
           <t>-</t>
@@ -54023,10 +55543,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1134</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -54194,10 +55716,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1132</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -54369,10 +55893,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1119</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -54544,10 +56070,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1129</v>
+      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
@@ -54715,10 +56243,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1022</v>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -54864,7 +56394,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1276</v>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -54979,7 +56511,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1171</v>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
